--- a/data/trans_camb/P1805_2016_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1805_2016_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,49</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,44</t>
+          <t>-1,31; 2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,43</t>
+          <t>-2,82; 0,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,85</t>
+          <t>-1,6; 0,76</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-25,28%</t>
+          <t>-26,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,16%</t>
+          <t>-14,76%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 175,51</t>
+          <t>-49,15; 161,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 12,65</t>
+          <t>-53,36; 13,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 33,06</t>
+          <t>-41,78; 28,67</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,53</t>
+          <t>0,55; 2,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,18</t>
+          <t>-0,85; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,48</t>
+          <t>0,2; 1,83</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 184,25</t>
+          <t>22,94; 195,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 37,62</t>
+          <t>-19,7; 57,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 63,58</t>
+          <t>5,56; 74,56</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,84</t>
+          <t>0,48; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,92</t>
+          <t>1,09; 5,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,79</t>
+          <t>1,38; 4,3</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>168,32%</t>
+          <t>150,75%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132,92%</t>
+          <t>123,95%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146,09%</t>
+          <t>134,33%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,72; 655,55</t>
+          <t>13,94; 583,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,63; 331,35</t>
+          <t>18,95; 320,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,28; 315,23</t>
+          <t>46,08; 290,66</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,38</t>
+          <t>0,73; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,2</t>
+          <t>-0,38; 1,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,56</t>
+          <t>0,42; 1,61</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,94; 147,73</t>
+          <t>34,82; 169,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 36,03</t>
+          <t>-8,6; 42,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 61,71</t>
+          <t>13,34; 65,33</t>
         </is>
       </c>
     </row>
